--- a/output/log/secondVersion/表5-1_影響地價區域因素分析明細表_已填.xlsx
+++ b/output/log/secondVersion/表5-1_影響地價區域因素分析明細表_已填.xlsx
@@ -1143,7 +1143,7 @@
         <t>【AI判定】容積率（P002-00 修正百分比）
 填寫值：6.25
 資料來源：比準地 P001-00 普通(3) ／ P002-00 稍劣(4)
-判定依據：查表：共5級、最大±25.0%、級距6.25%；(4−3)×6.25 = +6.25
+判定依據：查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = +6.25
 基準表項目ID：shulin.regional.far</t>
       </text>
     </comment>
@@ -1467,7 +1467,7 @@
         <t>【AI判定】主要道路寬度（P002-00 修正百分比）
 填寫值：15.0
 資料來源：比準地 P001-00 優(1) ／ P002-00 劣(5)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(5−1)×3.75 = +15.00
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = +15.00
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1494,7 +1494,7 @@
         <t>【AI判定】主要道路寬度（P003-00 修正百分比）
 填寫值：11.25
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍劣(4)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1521,7 +1521,7 @@
         <t>【AI判定】主要道路寬度（P004-00 修正百分比）
 填寫值：11.25
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍劣(4)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1566,7 +1566,7 @@
         <t>【AI判定】區段內道路平均寬度（P002-00 修正百分比）
 填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P002-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1593,7 +1593,7 @@
         <t>【AI判定】區段內道路平均寬度（P003-00 修正百分比）
 填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P003-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1620,7 +1620,7 @@
         <t>【AI判定】區段內道路平均寬度（P004-00 修正百分比）
 填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P004-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1665,7 +1665,7 @@
         <t>【AI判定】區段內道路規劃及闢建程度（P002-00 修正百分比）
 填寫值：2.5
 資料來源：比準地 P001-00 稍優(2) ／ P002-00 普通(3)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(3−2)×2.5 = +2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = +2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -1692,7 +1692,7 @@
         <t>【AI判定】區段內道路規劃及闢建程度（P003-00 修正百分比）
 填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P003-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -1719,7 +1719,7 @@
         <t>【AI判定】區段內道路規劃及闢建程度（P004-00 修正百分比）
 填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P004-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -5657,7 +5657,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>產生日期：2026-09-12　產生器：engine/export_xlsx.py</t>
+          <t>產生日期：2026-09-13　產生器：engine/export_xlsx.py</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±25.0%、級距6.25%；(4−3)×6.25 = +6.25</t>
+          <t>查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = +6.25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(5−1)×3.75 = +15.00</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = +15.00</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(3−2)×2.5 = +2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = +2.50</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">

--- a/output/log/secondVersion/表5-1_影響地價區域因素分析明細表_已填.xlsx
+++ b/output/log/secondVersion/表5-1_影響地價區域因素分析明細表_已填.xlsx
@@ -1143,7 +1143,7 @@
         <t>【AI判定】容積率（P002-00 修正百分比）
 填寫值：6.25
 資料來源：比準地 P001-00 普通(3) ／ P002-00 稍劣(4)
-判定依據：查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = +6.25
+判定依據：查表：共5級、最大±25.0%、級距6.25%；(4−3)×6.25 = +6.25
 基準表項目ID：shulin.regional.far</t>
       </text>
     </comment>
@@ -1467,7 +1467,7 @@
         <t>【AI判定】主要道路寬度（P002-00 修正百分比）
 填寫值：15.0
 資料來源：比準地 P001-00 優(1) ／ P002-00 劣(5)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = +15.00
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(5−1)×3.75 = +15.00
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1494,7 +1494,7 @@
         <t>【AI判定】主要道路寬度（P003-00 修正百分比）
 填寫值：11.25
 資料來源：比準地 P001-00 優(1) ／ P003-00 稍劣(4)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1521,7 +1521,7 @@
         <t>【AI判定】主要道路寬度（P004-00 修正百分比）
 填寫值：11.25
 資料來源：比準地 P001-00 優(1) ／ P004-00 稍劣(4)
-判定依據：查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25
+判定依據：查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25
 基準表項目ID：shulin.regional.main_road_width</t>
       </text>
     </comment>
@@ -1566,7 +1566,7 @@
         <t>【AI判定】區段內道路平均寬度（P002-00 修正百分比）
 填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P002-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1593,7 +1593,7 @@
         <t>【AI判定】區段內道路平均寬度（P003-00 修正百分比）
 填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P003-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1620,7 +1620,7 @@
         <t>【AI判定】區段內道路平均寬度（P004-00 修正百分比）
 填寫值：6.0
 資料來源：比準地 P001-00 普通(3) ／ P004-00 劣(5)
-判定依據：查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00
+判定依據：查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00
 基準表項目ID：shulin.regional.avg_road_width</t>
       </text>
     </comment>
@@ -1665,7 +1665,7 @@
         <t>【AI判定】區段內道路規劃及闢建程度（P002-00 修正百分比）
 填寫值：2.5
 資料來源：比準地 P001-00 稍優(2) ／ P002-00 普通(3)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = +2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(3−2)×2.5 = +2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -1692,7 +1692,7 @@
         <t>【AI判定】區段內道路規劃及闢建程度（P003-00 修正百分比）
 填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P003-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -1719,7 +1719,7 @@
         <t>【AI判定】區段內道路規劃及闢建程度（P004-00 修正百分比）
 填寫值：-2.5
 資料來源：比準地 P001-00 稍優(2) ／ P004-00 優(1)
-判定依據：查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50
+判定依據：查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50
 基準表項目ID：shulin.regional.road_dev</t>
       </text>
     </comment>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±25.0%、級距6.25%；(3−4)×6.25 = +6.25</t>
+          <t>查表：共5級、最大±25.0%、級距6.25%；(4−3)×6.25 = +6.25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(1−5)×3.75 = +15.00</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(5−1)×3.75 = +15.00</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±15.0%、級距3.75%；(1−4)×3.75 = +11.25</t>
+          <t>查表：共5級、最大±15.0%、級距3.75%；(4−1)×3.75 = +11.25</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±12.0%、級距3.0%；(3−5)×3.0 = +6.00</t>
+          <t>查表：共5級、最大±12.0%、級距3.0%；(5−3)×3.0 = +6.00</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−3)×2.5 = +2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(3−2)×2.5 = +2.50</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>查表：共5級、最大±10.0%、級距2.5%；(2−1)×2.5 = -2.50</t>
+          <t>查表：共5級、最大±10.0%、級距2.5%；(1−2)×2.5 = -2.50</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
